--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N62_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N62_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>4.952450840327153</v>
+        <v>0.8047732615531623</v>
       </c>
       <c r="D2" t="n">
-        <v>3.618959242846154</v>
+        <v>0.5880808769625</v>
       </c>
       <c r="E2" t="n">
-        <v>5.405054834396414</v>
+        <v>0.8783214105894173</v>
       </c>
       <c r="F2" t="n">
-        <v>5.843246526261723</v>
+        <v>0.9495275605175301</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.90505477973166</v>
+        <v>2.747071401706395</v>
       </c>
       <c r="D3" t="n">
-        <v>5.50205495269635</v>
+        <v>0.894083929813157</v>
       </c>
       <c r="E3" t="n">
-        <v>5.405054834396414</v>
+        <v>0.8783214105894173</v>
       </c>
       <c r="F3" t="n">
-        <v>5.843246526261723</v>
+        <v>0.9495275605175301</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>15.86000257388675</v>
+        <v>2.577250418256596</v>
       </c>
       <c r="D4" t="n">
-        <v>16.84815731091906</v>
+        <v>2.737825563024348</v>
       </c>
       <c r="E4" t="n">
-        <v>5.405054834396414</v>
+        <v>0.8783214105894173</v>
       </c>
       <c r="F4" t="n">
-        <v>5.843246526261723</v>
+        <v>0.9495275605175301</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
